--- a/xlsx/template@模板.xlsx
+++ b/xlsx/template@模板.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29725"/>
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Github\excelparser\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\Github\excelparser\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4171FE79-0742-450A-8251-1EC001C13680}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55595D26-B1EE-4673-9A8D-0A2F9A25435E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="595" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="85">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="84">
   <si>
     <t>int</t>
     <phoneticPr fontId="7" type="noConversion"/>
@@ -521,10 +521,6 @@
   </si>
   <si>
     <t>[3]any</t>
-    <phoneticPr fontId="7" type="noConversion"/>
-  </si>
-  <si>
-    <t>[2]any</t>
     <phoneticPr fontId="7" type="noConversion"/>
   </si>
   <si>
@@ -12424,7 +12420,7 @@
         <v>13</v>
       </c>
       <c r="C1" s="4" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D1" s="4" t="s">
         <v>3</v>
@@ -12580,16 +12576,16 @@
         <v>0</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C2" s="4" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="D2" s="4" t="s">
         <v>71</v>
       </c>
       <c r="E2" s="4" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F2" s="4" t="s">
         <v>0</v>
@@ -12712,7 +12708,7 @@
         <v>0</v>
       </c>
       <c r="AT2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="AU2" s="4" t="s">
         <v>0</v>
@@ -12763,7 +12759,7 @@
         <v>0</v>
       </c>
       <c r="BK2" s="4" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="BL2" s="4" t="s">
         <v>0</v>
@@ -12772,10 +12768,10 @@
         <v>2</v>
       </c>
       <c r="BN2" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="BO2" s="4" t="s">
         <v>79</v>
-      </c>
-      <c r="BO2" s="4" t="s">
-        <v>80</v>
       </c>
       <c r="BP2" s="4" t="s">
         <v>0</v>
@@ -12784,7 +12780,7 @@
         <v>2</v>
       </c>
       <c r="BR2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BS2" s="4" t="s">
         <v>0</v>
@@ -12793,13 +12789,13 @@
         <v>2</v>
       </c>
       <c r="BU2" s="4" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="BV2" s="4" t="s">
         <v>0</v>
       </c>
       <c r="BW2" s="4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="BX2" s="4" t="s">
         <v>0</v>
@@ -12811,10 +12807,10 @@
         <v>2</v>
       </c>
       <c r="CA2" s="4" t="s">
-        <v>72</v>
+        <v>78</v>
       </c>
       <c r="CB2" s="16" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="CC2" s="4" t="s">
         <v>0</v>
@@ -12823,7 +12819,7 @@
         <v>2</v>
       </c>
       <c r="CE2" s="16" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="CF2" s="4" t="s">
         <v>0</v>
@@ -13073,14 +13069,14 @@
         <v>1001</v>
       </c>
       <c r="B5" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C5" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D5" s="5"/>
       <c r="E5" s="20" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F5" s="5">
         <v>2</v>
@@ -13276,10 +13272,10 @@
         <v>1002</v>
       </c>
       <c r="B6" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C6" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D6" s="5"/>
       <c r="E6" s="5" t="s">
@@ -13479,10 +13475,10 @@
         <v>1003</v>
       </c>
       <c r="B7" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C7" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D7" s="5"/>
       <c r="E7" s="5" t="s">
@@ -13682,10 +13678,10 @@
         <v>1004</v>
       </c>
       <c r="B8" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C8" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D8" s="5"/>
       <c r="E8" s="5" t="s">
@@ -13885,10 +13881,10 @@
         <v>1005</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C9" s="5" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D9" s="5"/>
       <c r="E9" s="5" t="s">
